--- a/AAII_Financials/Quarterly/NAVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NAVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>NAVN</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,43 +656,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45777</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45688</v>
       </c>
       <c r="G7" s="2">
         <v>45596</v>
@@ -709,22 +710,25 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>164700</v>
+        <v>194900</v>
       </c>
       <c r="E8" s="3">
         <v>164700</v>
       </c>
       <c r="F8" s="3">
-        <v>141600</v>
+        <v>164700</v>
       </c>
       <c r="G8" s="3">
-        <v>141600</v>
+        <v>151100</v>
       </c>
       <c r="H8" s="3">
         <v>126900</v>
@@ -738,22 +742,25 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>46300</v>
+        <v>57100</v>
       </c>
       <c r="E9" s="3">
         <v>46300</v>
       </c>
       <c r="F9" s="3">
-        <v>43600</v>
+        <v>46300</v>
       </c>
       <c r="G9" s="3">
-        <v>43600</v>
+        <v>44500</v>
       </c>
       <c r="H9" s="3">
         <v>41300</v>
@@ -767,22 +774,25 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>118400</v>
+        <v>137900</v>
       </c>
       <c r="E10" s="3">
         <v>118400</v>
       </c>
       <c r="F10" s="3">
-        <v>97900</v>
+        <v>118400</v>
       </c>
       <c r="G10" s="3">
-        <v>97900</v>
+        <v>106600</v>
       </c>
       <c r="H10" s="3">
         <v>85600</v>
@@ -796,8 +806,11 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,22 +822,23 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>32400</v>
+        <v>51200</v>
       </c>
       <c r="E12" s="3">
         <v>32400</v>
       </c>
       <c r="F12" s="3">
-        <v>32300</v>
+        <v>32400</v>
       </c>
       <c r="G12" s="3">
-        <v>32300</v>
+        <v>33000</v>
       </c>
       <c r="H12" s="3">
         <v>28900</v>
@@ -838,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,19 +884,22 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>10300</v>
+        <v>97500</v>
       </c>
       <c r="E14" s="3">
         <v>10300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>10300</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -896,13 +916,16 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="E15" s="3">
         <v>2400</v>
@@ -911,7 +934,7 @@
         <v>2400</v>
       </c>
       <c r="G15" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="H15" s="3">
         <v>2600</v>
@@ -925,8 +948,11 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,22 +961,23 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>178800</v>
+        <v>274200</v>
       </c>
       <c r="E17" s="3">
         <v>178800</v>
       </c>
       <c r="F17" s="3">
-        <v>167700</v>
+        <v>178800</v>
       </c>
       <c r="G17" s="3">
-        <v>167700</v>
+        <v>170600</v>
       </c>
       <c r="H17" s="3">
         <v>154500</v>
@@ -964,22 +991,25 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-14100</v>
+        <v>-79200</v>
       </c>
       <c r="E18" s="3">
         <v>-14100</v>
       </c>
       <c r="F18" s="3">
-        <v>-26100</v>
+        <v>-14100</v>
       </c>
       <c r="G18" s="3">
-        <v>-26100</v>
+        <v>-19500</v>
       </c>
       <c r="H18" s="3">
         <v>-27700</v>
@@ -993,8 +1023,11 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,22 +1039,23 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5200</v>
+        <v>30700</v>
       </c>
       <c r="E20" s="3">
         <v>5200</v>
       </c>
       <c r="F20" s="3">
-        <v>-4800</v>
+        <v>5200</v>
       </c>
       <c r="G20" s="3">
-        <v>-4800</v>
+        <v>-700</v>
       </c>
       <c r="H20" s="3">
         <v>-1200</v>
@@ -1035,22 +1069,25 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-16900</v>
+        <v>-107800</v>
       </c>
       <c r="E21" s="3">
         <v>-16900</v>
       </c>
       <c r="F21" s="3">
-        <v>-18900</v>
+        <v>-16900</v>
       </c>
       <c r="G21" s="3">
-        <v>-18900</v>
+        <v>-16700</v>
       </c>
       <c r="H21" s="3">
         <v>-23800</v>
@@ -1064,22 +1101,25 @@
       <c r="K21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>16000</v>
+        <v>15500</v>
       </c>
       <c r="E22" s="3">
         <v>16000</v>
       </c>
       <c r="F22" s="3">
-        <v>19100</v>
+        <v>16000</v>
       </c>
       <c r="G22" s="3">
-        <v>19100</v>
+        <v>19700</v>
       </c>
       <c r="H22" s="3">
         <v>18900</v>
@@ -1093,22 +1133,25 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-45900</v>
+        <v>-221900</v>
       </c>
       <c r="E23" s="3">
         <v>-45900</v>
       </c>
       <c r="F23" s="3">
-        <v>-41600</v>
+        <v>-45900</v>
       </c>
       <c r="G23" s="3">
-        <v>-41600</v>
+        <v>-36700</v>
       </c>
       <c r="H23" s="3">
         <v>-44100</v>
@@ -1122,22 +1165,25 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E24" s="3">
         <v>4000</v>
       </c>
       <c r="F24" s="3">
-        <v>2600</v>
+        <v>4000</v>
       </c>
       <c r="G24" s="3">
-        <v>2600</v>
+        <v>5200</v>
       </c>
       <c r="H24" s="3">
         <v>2100</v>
@@ -1151,8 +1197,11 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,22 +1229,25 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-49900</v>
+        <v>-225400</v>
       </c>
       <c r="E26" s="3">
         <v>-49900</v>
       </c>
       <c r="F26" s="3">
-        <v>-44300</v>
+        <v>-49900</v>
       </c>
       <c r="G26" s="3">
-        <v>-44300</v>
+        <v>-41900</v>
       </c>
       <c r="H26" s="3">
         <v>-46300</v>
@@ -1209,22 +1261,25 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-49900</v>
+        <v>-225400</v>
       </c>
       <c r="E27" s="3">
         <v>-49900</v>
       </c>
       <c r="F27" s="3">
-        <v>-44300</v>
+        <v>-49900</v>
       </c>
       <c r="G27" s="3">
-        <v>-44300</v>
+        <v>-41900</v>
       </c>
       <c r="H27" s="3">
         <v>-46300</v>
@@ -1238,8 +1293,11 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,22 +1421,25 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5200</v>
+        <v>-30700</v>
       </c>
       <c r="E32" s="3">
         <v>-5200</v>
       </c>
       <c r="F32" s="3">
-        <v>4800</v>
+        <v>-5200</v>
       </c>
       <c r="G32" s="3">
-        <v>4800</v>
+        <v>700</v>
       </c>
       <c r="H32" s="3">
         <v>1200</v>
@@ -1383,22 +1453,25 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-49900</v>
+        <v>-225400</v>
       </c>
       <c r="E33" s="3">
         <v>-49900</v>
       </c>
       <c r="F33" s="3">
-        <v>-44300</v>
+        <v>-49900</v>
       </c>
       <c r="G33" s="3">
-        <v>-44300</v>
+        <v>-41900</v>
       </c>
       <c r="H33" s="3">
         <v>-46300</v>
@@ -1412,8 +1485,11 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,22 +1517,25 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-49900</v>
+        <v>-225400</v>
       </c>
       <c r="E35" s="3">
         <v>-49900</v>
       </c>
       <c r="F35" s="3">
-        <v>-44300</v>
+        <v>-49900</v>
       </c>
       <c r="G35" s="3">
-        <v>-44300</v>
+        <v>-41900</v>
       </c>
       <c r="H35" s="3">
         <v>-46300</v>
@@ -1470,24 +1549,27 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45777</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45688</v>
       </c>
       <c r="G38" s="2">
         <v>45596</v>
@@ -1504,8 +1586,11 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,22 +1616,23 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>223200</v>
+        <v>809100</v>
       </c>
       <c r="E41" s="3">
         <v>223200</v>
       </c>
       <c r="F41" s="3">
-        <v>157700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>157700</v>
+        <v>223200</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1559,8 +1646,11 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,22 +1678,25 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>352200</v>
+        <v>423400</v>
       </c>
       <c r="E43" s="3">
         <v>352200</v>
       </c>
       <c r="F43" s="3">
-        <v>345800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>345800</v>
+        <v>352200</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1617,8 +1710,11 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1646,22 +1742,25 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>36200</v>
+        <v>43800</v>
       </c>
       <c r="E45" s="3">
         <v>36200</v>
       </c>
       <c r="F45" s="3">
-        <v>20300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>20300</v>
+        <v>36200</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1675,22 +1774,25 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>718900</v>
+        <v>1378400</v>
       </c>
       <c r="E46" s="3">
         <v>718900</v>
       </c>
       <c r="F46" s="3">
-        <v>688900</v>
-      </c>
-      <c r="G46" s="3">
-        <v>688900</v>
+        <v>718900</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1704,8 +1806,11 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1733,22 +1838,25 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>74500</v>
+        <v>74400</v>
       </c>
       <c r="E48" s="3">
         <v>74500</v>
       </c>
       <c r="F48" s="3">
-        <v>77500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>77500</v>
+        <v>74500</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1762,22 +1870,25 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>291000</v>
+        <v>287500</v>
       </c>
       <c r="E49" s="3">
         <v>291000</v>
       </c>
       <c r="F49" s="3">
-        <v>275400</v>
+        <v>291000</v>
       </c>
       <c r="G49" s="3">
-        <v>275400</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -1791,8 +1902,11 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,22 +1966,25 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>29000</v>
+        <v>29700</v>
       </c>
       <c r="E52" s="3">
         <v>29000</v>
       </c>
       <c r="F52" s="3">
-        <v>26000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>26000</v>
+        <v>29000</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1878,8 +1998,11 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,22 +2030,25 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1134400</v>
+        <v>1792700</v>
       </c>
       <c r="E54" s="3">
         <v>1134400</v>
       </c>
       <c r="F54" s="3">
-        <v>1084000</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1084000</v>
+        <v>1134400</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1936,8 +2062,11 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,22 +2092,23 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>48200</v>
+        <v>62300</v>
       </c>
       <c r="E57" s="3">
         <v>48200</v>
       </c>
       <c r="F57" s="3">
-        <v>42800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>42800</v>
+        <v>48200</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -1991,22 +2122,25 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12700</v>
+        <v>11500</v>
       </c>
       <c r="E58" s="3">
         <v>12700</v>
       </c>
       <c r="F58" s="3">
-        <v>232300</v>
+        <v>12700</v>
       </c>
       <c r="G58" s="3">
-        <v>232300</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2020,22 +2154,25 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>114900</v>
+        <v>126600</v>
       </c>
       <c r="E59" s="3">
         <v>114900</v>
       </c>
       <c r="F59" s="3">
-        <v>98500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>98500</v>
+        <v>114900</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2049,22 +2186,25 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>249200</v>
+        <v>307100</v>
       </c>
       <c r="E60" s="3">
         <v>249200</v>
       </c>
       <c r="F60" s="3">
-        <v>446000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>446000</v>
+        <v>249200</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2078,22 +2218,25 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>697900</v>
+        <v>242800</v>
       </c>
       <c r="E61" s="3">
         <v>697900</v>
       </c>
       <c r="F61" s="3">
-        <v>440100</v>
+        <v>697900</v>
       </c>
       <c r="G61" s="3">
-        <v>440100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2107,22 +2250,25 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>85300</v>
+        <v>15900</v>
       </c>
       <c r="E62" s="3">
         <v>85300</v>
       </c>
       <c r="F62" s="3">
-        <v>75100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>75100</v>
+        <v>85300</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2136,8 +2282,11 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,22 +2378,25 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1041700</v>
+        <v>573800</v>
       </c>
       <c r="E66" s="3">
         <v>1041700</v>
       </c>
       <c r="F66" s="3">
-        <v>969700</v>
-      </c>
-      <c r="G66" s="3">
-        <v>969700</v>
+        <v>1041700</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2252,8 +2410,11 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,13 +2488,16 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1301100</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>1301100</v>
@@ -2338,7 +2506,7 @@
         <v>1301100</v>
       </c>
       <c r="G70" s="3">
-        <v>1301100</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,22 +2552,25 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1717000</v>
+        <v>-1942400</v>
       </c>
       <c r="E72" s="3">
         <v>-1717000</v>
       </c>
       <c r="F72" s="3">
-        <v>-1617100</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1617100</v>
+        <v>-1717000</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2410,8 +2584,11 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,22 +2680,25 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-1208500</v>
+        <v>1218800</v>
       </c>
       <c r="E76" s="3">
         <v>-1208500</v>
       </c>
       <c r="F76" s="3">
-        <v>-1186900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-1186900</v>
+        <v>-1208500</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2526,8 +2712,11 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,24 +2744,27 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45777</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45688</v>
       </c>
       <c r="G80" s="2">
         <v>45596</v>
@@ -2589,22 +2781,25 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-49900</v>
+        <v>-225400</v>
       </c>
       <c r="E81" s="3">
         <v>-49900</v>
       </c>
       <c r="F81" s="3">
-        <v>-44300</v>
+        <v>-49900</v>
       </c>
       <c r="G81" s="3">
-        <v>-44300</v>
+        <v>-41900</v>
       </c>
       <c r="H81" s="3">
         <v>-46300</v>
@@ -2618,8 +2813,11 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,8 +2829,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2660,8 +2859,11 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,22 +3019,25 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2400</v>
+        <v>-6100</v>
       </c>
       <c r="E89" s="3">
         <v>2400</v>
       </c>
       <c r="F89" s="3">
-        <v>-10700</v>
+        <v>2400</v>
       </c>
       <c r="G89" s="3">
-        <v>-10700</v>
+        <v>-12400</v>
       </c>
       <c r="H89" s="3">
         <v>-14500</v>
@@ -2834,8 +3051,11 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,19 +3067,20 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-200</v>
@@ -2876,8 +3097,11 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,22 +3161,25 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5500</v>
+        <v>-38500</v>
       </c>
       <c r="E94" s="3">
         <v>-5500</v>
       </c>
       <c r="F94" s="3">
-        <v>9400</v>
+        <v>-5500</v>
       </c>
       <c r="G94" s="3">
-        <v>9400</v>
+        <v>-23200</v>
       </c>
       <c r="H94" s="3">
         <v>13000</v>
@@ -2963,8 +3193,11 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3209,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3239,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,22 +3335,25 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>3300</v>
+        <v>624000</v>
       </c>
       <c r="E100" s="3">
         <v>3300</v>
       </c>
       <c r="F100" s="3">
-        <v>600</v>
+        <v>3300</v>
       </c>
       <c r="G100" s="3">
-        <v>600</v>
+        <v>26300</v>
       </c>
       <c r="H100" s="3">
         <v>25700</v>
@@ -3121,8 +3367,11 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,22 +3399,25 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2500</v>
+        <v>579700</v>
       </c>
       <c r="E102" s="3">
         <v>2500</v>
       </c>
       <c r="F102" s="3">
-        <v>-2400</v>
+        <v>2500</v>
       </c>
       <c r="G102" s="3">
-        <v>-2400</v>
+        <v>-9400</v>
       </c>
       <c r="H102" s="3">
         <v>24000</v>
@@ -3177,6 +3429,9 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NAVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NAVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>NAVN</t>
   </si>
@@ -656,161 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45961</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
-        <v>45412</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>177900</v>
+      </c>
+      <c r="E8" s="3">
         <v>194900</v>
-      </c>
-      <c r="E8" s="3">
-        <v>164700</v>
       </c>
       <c r="F8" s="3">
         <v>164700</v>
       </c>
       <c r="G8" s="3">
+        <v>164700</v>
+      </c>
+      <c r="H8" s="3">
+        <v>132000</v>
+      </c>
+      <c r="I8" s="3">
         <v>151100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>126900</v>
       </c>
-      <c r="I8" s="3">
-        <v>126900</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E9" s="3">
         <v>57100</v>
-      </c>
-      <c r="E9" s="3">
-        <v>46300</v>
       </c>
       <c r="F9" s="3">
         <v>46300</v>
       </c>
       <c r="G9" s="3">
+        <v>46300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>42700</v>
+      </c>
+      <c r="I9" s="3">
         <v>44500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>41300</v>
       </c>
-      <c r="I9" s="3">
-        <v>41300</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>125800</v>
+      </c>
+      <c r="E10" s="3">
         <v>137900</v>
-      </c>
-      <c r="E10" s="3">
-        <v>118400</v>
       </c>
       <c r="F10" s="3">
         <v>118400</v>
       </c>
       <c r="G10" s="3">
+        <v>118400</v>
+      </c>
+      <c r="H10" s="3">
+        <v>89200</v>
+      </c>
+      <c r="I10" s="3">
         <v>106600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>85600</v>
       </c>
-      <c r="I10" s="3">
-        <v>85600</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,40 +835,44 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E12" s="3">
         <v>51200</v>
-      </c>
-      <c r="E12" s="3">
-        <v>32400</v>
       </c>
       <c r="F12" s="3">
         <v>32400</v>
       </c>
       <c r="G12" s="3">
+        <v>32400</v>
+      </c>
+      <c r="H12" s="3">
+        <v>31600</v>
+      </c>
+      <c r="I12" s="3">
         <v>33000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>28900</v>
       </c>
-      <c r="I12" s="3">
-        <v>28900</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,22 +903,25 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E14" s="3">
         <v>97500</v>
-      </c>
-      <c r="E14" s="3">
-        <v>10300</v>
       </c>
       <c r="F14" s="3">
         <v>10300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>10300</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -919,40 +938,46 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E15" s="3">
         <v>2100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2400</v>
       </c>
       <c r="F15" s="3">
         <v>2400</v>
       </c>
       <c r="G15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I15" s="3">
         <v>2100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>2600</v>
       </c>
-      <c r="I15" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +987,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>259300</v>
+      </c>
+      <c r="E17" s="3">
         <v>274200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>178800</v>
       </c>
       <c r="F17" s="3">
         <v>178800</v>
       </c>
       <c r="G17" s="3">
+        <v>178800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>164800</v>
+      </c>
+      <c r="I17" s="3">
         <v>170600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>154500</v>
       </c>
-      <c r="I17" s="3">
-        <v>154500</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-79200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-14100</v>
       </c>
       <c r="F18" s="3">
         <v>-14100</v>
       </c>
       <c r="G18" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-19500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-27700</v>
       </c>
-      <c r="I18" s="3">
-        <v>-27700</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,168 +1072,184 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E20" s="3">
         <v>30700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>5200</v>
       </c>
       <c r="F20" s="3">
         <v>5200</v>
       </c>
       <c r="G20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-107800</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-16900</v>
       </c>
       <c r="F21" s="3">
         <v>-16900</v>
       </c>
       <c r="G21" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-16700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-23800</v>
       </c>
-      <c r="I21" s="3">
-        <v>-23800</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E22" s="3">
         <v>15500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>16000</v>
       </c>
       <c r="F22" s="3">
         <v>16000</v>
       </c>
       <c r="G22" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I22" s="3">
         <v>19700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>18900</v>
       </c>
-      <c r="I22" s="3">
-        <v>18900</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-82200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-221900</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-45900</v>
       </c>
       <c r="F23" s="3">
         <v>-45900</v>
       </c>
       <c r="G23" s="3">
+        <v>-45900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-36700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-44100</v>
       </c>
-      <c r="I23" s="3">
-        <v>-44100</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E24" s="3">
         <v>3500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>4000</v>
       </c>
       <c r="F24" s="3">
         <v>4000</v>
       </c>
       <c r="G24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>5200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1280,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-225400</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-49900</v>
       </c>
       <c r="F26" s="3">
         <v>-49900</v>
       </c>
       <c r="G26" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-41900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-46300</v>
       </c>
-      <c r="I26" s="3">
-        <v>-46300</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-225400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-49900</v>
       </c>
       <c r="F27" s="3">
         <v>-49900</v>
       </c>
       <c r="G27" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-41900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-46300</v>
       </c>
-      <c r="I27" s="3">
-        <v>-46300</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1385,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1420,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1455,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1490,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-30700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-5200</v>
       </c>
       <c r="F32" s="3">
         <v>-5200</v>
       </c>
       <c r="G32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-225400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-49900</v>
       </c>
       <c r="F33" s="3">
         <v>-49900</v>
       </c>
       <c r="G33" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-41900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-46300</v>
       </c>
-      <c r="I33" s="3">
-        <v>-46300</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1595,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-225400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-49900</v>
       </c>
       <c r="F35" s="3">
         <v>-49900</v>
       </c>
       <c r="G35" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-41900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-46300</v>
       </c>
-      <c r="I35" s="3">
-        <v>-46300</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45961</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
-        <v>45412</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1687,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,25 +1702,26 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>583500</v>
+      </c>
+      <c r="E41" s="3">
         <v>809100</v>
-      </c>
-      <c r="E41" s="3">
-        <v>223200</v>
       </c>
       <c r="F41" s="3">
         <v>223200</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+      <c r="G41" s="3">
+        <v>223200</v>
+      </c>
+      <c r="H41" s="3">
+        <v>157700</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1649,13 +1735,16 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1681,25 +1770,28 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>426400</v>
+      </c>
+      <c r="E43" s="3">
         <v>423400</v>
-      </c>
-      <c r="E43" s="3">
-        <v>352200</v>
       </c>
       <c r="F43" s="3">
         <v>352200</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>352200</v>
+      </c>
+      <c r="H43" s="3">
+        <v>345800</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1713,8 +1805,11 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1745,25 +1840,28 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E45" s="3">
         <v>43800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>36200</v>
       </c>
       <c r="F45" s="3">
         <v>36200</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="G45" s="3">
+        <v>36200</v>
+      </c>
+      <c r="H45" s="3">
+        <v>20300</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1777,25 +1875,28 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1307000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1378400</v>
-      </c>
-      <c r="E46" s="3">
-        <v>718900</v>
       </c>
       <c r="F46" s="3">
         <v>718900</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+      <c r="G46" s="3">
+        <v>718900</v>
+      </c>
+      <c r="H46" s="3">
+        <v>688900</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1809,8 +1910,11 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1841,25 +1945,28 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E48" s="3">
         <v>74400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>74500</v>
       </c>
       <c r="F48" s="3">
         <v>74500</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+      <c r="G48" s="3">
+        <v>74500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>77500</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -1873,31 +1980,34 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E49" s="3">
         <v>287500</v>
-      </c>
-      <c r="E49" s="3">
-        <v>291000</v>
       </c>
       <c r="F49" s="3">
         <v>291000</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>291000</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>275400</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1905,8 +2015,11 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2050,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,25 +2085,28 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E52" s="3">
         <v>29700</v>
-      </c>
-      <c r="E52" s="3">
-        <v>29000</v>
       </c>
       <c r="F52" s="3">
         <v>29000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3">
+        <v>29000</v>
+      </c>
+      <c r="H52" s="3">
+        <v>26000</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2001,8 +2120,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,25 +2155,28 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1708800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1792700</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1134400</v>
       </c>
       <c r="F54" s="3">
         <v>1134400</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+      <c r="G54" s="3">
+        <v>1134400</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1084000</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2065,8 +2190,11 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2207,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,25 +2222,26 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E57" s="3">
         <v>62300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>48200</v>
       </c>
       <c r="F57" s="3">
         <v>48200</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+      <c r="G57" s="3">
+        <v>48200</v>
+      </c>
+      <c r="H57" s="3">
+        <v>42800</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2125,31 +2255,34 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E58" s="3">
         <v>11500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>12700</v>
       </c>
       <c r="F58" s="3">
         <v>12700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>232300</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2157,25 +2290,28 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>156100</v>
+      </c>
+      <c r="E59" s="3">
         <v>126600</v>
-      </c>
-      <c r="E59" s="3">
-        <v>114900</v>
       </c>
       <c r="F59" s="3">
         <v>114900</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+      <c r="G59" s="3">
+        <v>114900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>108400</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2189,25 +2325,28 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>320900</v>
+      </c>
+      <c r="E60" s="3">
         <v>307100</v>
-      </c>
-      <c r="E60" s="3">
-        <v>249200</v>
       </c>
       <c r="F60" s="3">
         <v>249200</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+      <c r="G60" s="3">
+        <v>249200</v>
+      </c>
+      <c r="H60" s="3">
+        <v>446000</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2221,25 +2360,28 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>161800</v>
+      </c>
+      <c r="E61" s="3">
         <v>242800</v>
-      </c>
-      <c r="E61" s="3">
-        <v>697900</v>
       </c>
       <c r="F61" s="3">
         <v>697900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>697900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>440100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2253,25 +2395,28 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E62" s="3">
         <v>15900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>85300</v>
       </c>
       <c r="F62" s="3">
         <v>85300</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>85300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>75100</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2285,8 +2430,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2465,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2500,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,25 +2535,28 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>500700</v>
+      </c>
+      <c r="E66" s="3">
         <v>573800</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1041700</v>
       </c>
       <c r="F66" s="3">
         <v>1041700</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+      <c r="G66" s="3">
+        <v>1041700</v>
+      </c>
+      <c r="H66" s="3">
+        <v>969700</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2413,8 +2570,11 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2587,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2620,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2655,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2500,19 +2667,19 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>1301100</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
         <v>1301100</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>1301100</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>1301100</v>
       </c>
       <c r="I70" s="3">
-        <v>1301100</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -2523,8 +2690,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,25 +2725,28 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2015100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1942400</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-1717000</v>
       </c>
       <c r="F72" s="3">
         <v>-1717000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+      <c r="G72" s="3">
+        <v>-1717000</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-1617100</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2587,8 +2760,11 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2795,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2830,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,28 +2865,31 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1208100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1218800</v>
-      </c>
-      <c r="E76" s="3">
-        <v>-1208500</v>
       </c>
       <c r="F76" s="3">
         <v>-1208500</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-1082000</v>
+      <c r="G76" s="3">
+        <v>-1208500</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-1186900</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2715,8 +2900,11 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2935,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45961</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
-        <v>45412</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-225400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-49900</v>
       </c>
       <c r="F81" s="3">
         <v>-49900</v>
       </c>
       <c r="G81" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-41900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-46300</v>
       </c>
-      <c r="I81" s="3">
-        <v>-46300</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,8 +3027,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2839,13 +3037,13 @@
         <v>1300</v>
       </c>
       <c r="E83" s="3">
+        <v>800</v>
+      </c>
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>1300</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2862,8 +3060,11 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3095,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3130,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3165,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3200,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3235,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6100</v>
-      </c>
-      <c r="E89" s="3">
-        <v>2400</v>
       </c>
       <c r="F89" s="3">
         <v>2400</v>
       </c>
       <c r="G89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-12400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-14500</v>
       </c>
-      <c r="I89" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3287,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3355,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3390,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-153500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-38500</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-5500</v>
       </c>
       <c r="F94" s="3">
         <v>-5500</v>
       </c>
       <c r="G94" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="H94" s="3">
+        <v>42000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-23200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>13000</v>
       </c>
-      <c r="I94" s="3">
-        <v>13000</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3442,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3475,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3510,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3545,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,55 +3580,61 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-110700</v>
+      </c>
+      <c r="E100" s="3">
         <v>624000</v>
-      </c>
-      <c r="E100" s="3">
-        <v>3300</v>
       </c>
       <c r="F100" s="3">
         <v>3300</v>
       </c>
       <c r="G100" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="I100" s="3">
         <v>26300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>25700</v>
       </c>
-      <c r="I100" s="3">
-        <v>25700</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3402,36 +3650,42 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-227200</v>
+      </c>
+      <c r="E102" s="3">
         <v>579700</v>
-      </c>
-      <c r="E102" s="3">
-        <v>2500</v>
       </c>
       <c r="F102" s="3">
         <v>2500</v>
       </c>
       <c r="G102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H102" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I102" s="3">
         <v>-9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>24000</v>
       </c>
-      <c r="I102" s="3">
-        <v>24000</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>0</v>
       </c>
     </row>
